--- a/files/mads_budget.xlsx
+++ b/files/mads_budget.xlsx
@@ -34,7 +34,7 @@
     </comment>
     <comment ref="A7" authorId="0">
       <text>
-        <t>Synkroniseret fra skatteberegner</t>
+        <t>Din månedlige løn efter skat. Dette er det beløb, der udbetales til dig efter alle skatter og fradrag er trukket fra.</t>
       </text>
     </comment>
     <comment ref="A8" authorId="0">
@@ -899,40 +899,40 @@
         <v>Løn, efter skat</v>
       </c>
       <c r="B7" s="1">
-        <v>15798274677</v>
+        <v>20293</v>
       </c>
       <c r="C7" s="1">
-        <v>15798274677</v>
+        <v>20293</v>
       </c>
       <c r="D7" s="1">
-        <v>15798274677</v>
+        <v>20293</v>
       </c>
       <c r="E7" s="1">
-        <v>15798274677</v>
+        <v>20293</v>
       </c>
       <c r="F7" s="1">
-        <v>15798274677</v>
+        <v>20293</v>
       </c>
       <c r="G7" s="1">
-        <v>15798274677</v>
+        <v>20293</v>
       </c>
       <c r="H7" s="1">
-        <v>15798274677</v>
+        <v>20293</v>
       </c>
       <c r="I7" s="1">
-        <v>15798274677</v>
+        <v>20293</v>
       </c>
       <c r="J7" s="1">
-        <v>15798274677</v>
+        <v>20293</v>
       </c>
       <c r="K7" s="1">
-        <v>15798274677</v>
+        <v>20293</v>
       </c>
       <c r="L7" s="1">
-        <v>15798274677</v>
+        <v>20293</v>
       </c>
       <c r="M7" s="1">
-        <v>15798274677</v>
+        <v>20293</v>
       </c>
       <c r="N7" s="1">
         <f>=SUM(B7:M7)</f>
@@ -1250,41 +1250,41 @@
       <c r="A15" t="str">
         <v>Husleje</v>
       </c>
-      <c r="B15" t="str">
-        <v/>
-      </c>
-      <c r="C15" t="str">
-        <v/>
-      </c>
-      <c r="D15" t="str">
-        <v/>
-      </c>
-      <c r="E15" t="str">
-        <v/>
-      </c>
-      <c r="F15" t="str">
-        <v/>
-      </c>
-      <c r="G15" t="str">
-        <v/>
-      </c>
-      <c r="H15" t="str">
-        <v/>
-      </c>
-      <c r="I15" t="str">
-        <v/>
-      </c>
-      <c r="J15" t="str">
-        <v/>
-      </c>
-      <c r="K15" t="str">
-        <v/>
-      </c>
-      <c r="L15" t="str">
-        <v/>
-      </c>
-      <c r="M15" t="str">
-        <v/>
+      <c r="B15" s="1">
+        <v>5500</v>
+      </c>
+      <c r="C15" s="1">
+        <v>5500</v>
+      </c>
+      <c r="D15" s="1">
+        <v>5500</v>
+      </c>
+      <c r="E15" s="1">
+        <v>5500</v>
+      </c>
+      <c r="F15" s="1">
+        <v>5500</v>
+      </c>
+      <c r="G15" s="1">
+        <v>5500</v>
+      </c>
+      <c r="H15" s="1">
+        <v>5500</v>
+      </c>
+      <c r="I15" s="1">
+        <v>5500</v>
+      </c>
+      <c r="J15" s="1">
+        <v>5500</v>
+      </c>
+      <c r="K15" s="1">
+        <v>5500</v>
+      </c>
+      <c r="L15" s="1">
+        <v>5500</v>
+      </c>
+      <c r="M15" s="1">
+        <v>5500</v>
       </c>
       <c r="N15" s="1">
         <f>=SUM(B15:M15)</f>
@@ -1468,43 +1468,43 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Vand</v>
-      </c>
-      <c r="B20" t="str">
-        <v/>
-      </c>
-      <c r="C20" t="str">
-        <v/>
-      </c>
-      <c r="D20" t="str">
-        <v/>
-      </c>
-      <c r="E20" t="str">
-        <v/>
-      </c>
-      <c r="F20" t="str">
-        <v/>
-      </c>
-      <c r="G20" t="str">
-        <v/>
-      </c>
-      <c r="H20" t="str">
-        <v/>
-      </c>
-      <c r="I20" t="str">
-        <v/>
-      </c>
-      <c r="J20" t="str">
-        <v/>
-      </c>
-      <c r="K20" t="str">
-        <v/>
-      </c>
-      <c r="L20" t="str">
-        <v/>
-      </c>
-      <c r="M20" t="str">
-        <v/>
+        <v>El/Vand</v>
+      </c>
+      <c r="B20" s="1">
+        <v>800</v>
+      </c>
+      <c r="C20" s="1">
+        <v>800</v>
+      </c>
+      <c r="D20" s="1">
+        <v>800</v>
+      </c>
+      <c r="E20" s="1">
+        <v>800</v>
+      </c>
+      <c r="F20" s="1">
+        <v>800</v>
+      </c>
+      <c r="G20" s="1">
+        <v>800</v>
+      </c>
+      <c r="H20" s="1">
+        <v>800</v>
+      </c>
+      <c r="I20" s="1">
+        <v>800</v>
+      </c>
+      <c r="J20" s="1">
+        <v>800</v>
+      </c>
+      <c r="K20" s="1">
+        <v>800</v>
+      </c>
+      <c r="L20" s="1">
+        <v>800</v>
+      </c>
+      <c r="M20" s="1">
+        <v>800</v>
       </c>
       <c r="N20" s="1">
         <f>=SUM(B20:M20)</f>
@@ -1998,41 +1998,41 @@
       <c r="A32" t="str">
         <v>Billån</v>
       </c>
-      <c r="B32" t="str">
-        <v/>
-      </c>
-      <c r="C32" t="str">
-        <v/>
-      </c>
-      <c r="D32" t="str">
-        <v/>
-      </c>
-      <c r="E32" t="str">
-        <v/>
-      </c>
-      <c r="F32" t="str">
-        <v/>
-      </c>
-      <c r="G32" t="str">
-        <v/>
-      </c>
-      <c r="H32" t="str">
-        <v/>
-      </c>
-      <c r="I32" t="str">
-        <v/>
-      </c>
-      <c r="J32" t="str">
-        <v/>
-      </c>
-      <c r="K32" t="str">
-        <v/>
-      </c>
-      <c r="L32" t="str">
-        <v/>
-      </c>
-      <c r="M32" t="str">
-        <v/>
+      <c r="B32" s="1">
+        <v>1200</v>
+      </c>
+      <c r="C32" s="1">
+        <v>1200</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1200</v>
+      </c>
+      <c r="E32" s="1">
+        <v>1200</v>
+      </c>
+      <c r="F32" s="1">
+        <v>1200</v>
+      </c>
+      <c r="G32" s="1">
+        <v>1200</v>
+      </c>
+      <c r="H32" s="1">
+        <v>1200</v>
+      </c>
+      <c r="I32" s="1">
+        <v>1200</v>
+      </c>
+      <c r="J32" s="1">
+        <v>1200</v>
+      </c>
+      <c r="K32" s="1">
+        <v>1200</v>
+      </c>
+      <c r="L32" s="1">
+        <v>1200</v>
+      </c>
+      <c r="M32" s="1">
+        <v>1200</v>
       </c>
       <c r="N32" s="1">
         <f>=SUM(B32:M32)</f>
@@ -2392,43 +2392,43 @@
     </row>
     <row r="41">
       <c r="A41" t="str">
-        <v>Hybridnet/kabel-TV</v>
-      </c>
-      <c r="B41" t="str">
-        <v/>
-      </c>
-      <c r="C41" t="str">
-        <v/>
-      </c>
-      <c r="D41" t="str">
-        <v/>
-      </c>
-      <c r="E41" t="str">
-        <v/>
-      </c>
-      <c r="F41" t="str">
-        <v/>
-      </c>
-      <c r="G41" t="str">
-        <v/>
-      </c>
-      <c r="H41" t="str">
-        <v/>
-      </c>
-      <c r="I41" t="str">
-        <v/>
-      </c>
-      <c r="J41" t="str">
-        <v/>
-      </c>
-      <c r="K41" t="str">
-        <v/>
-      </c>
-      <c r="L41" t="str">
-        <v/>
-      </c>
-      <c r="M41" t="str">
-        <v/>
+        <v>Medier</v>
+      </c>
+      <c r="B41" s="1">
+        <v>300</v>
+      </c>
+      <c r="C41" s="1">
+        <v>300</v>
+      </c>
+      <c r="D41" s="1">
+        <v>300</v>
+      </c>
+      <c r="E41" s="1">
+        <v>300</v>
+      </c>
+      <c r="F41" s="1">
+        <v>300</v>
+      </c>
+      <c r="G41" s="1">
+        <v>300</v>
+      </c>
+      <c r="H41" s="1">
+        <v>300</v>
+      </c>
+      <c r="I41" s="1">
+        <v>300</v>
+      </c>
+      <c r="J41" s="1">
+        <v>300</v>
+      </c>
+      <c r="K41" s="1">
+        <v>300</v>
+      </c>
+      <c r="L41" s="1">
+        <v>300</v>
+      </c>
+      <c r="M41" s="1">
+        <v>300</v>
       </c>
       <c r="N41" s="1">
         <f>=SUM(B41:M41)</f>
@@ -2570,41 +2570,41 @@
       <c r="A45" t="str">
         <v>Fagforening</v>
       </c>
-      <c r="B45" t="str">
-        <v/>
-      </c>
-      <c r="C45" t="str">
-        <v/>
-      </c>
-      <c r="D45" t="str">
-        <v/>
-      </c>
-      <c r="E45" t="str">
-        <v/>
-      </c>
-      <c r="F45" t="str">
-        <v/>
-      </c>
-      <c r="G45" t="str">
-        <v/>
-      </c>
-      <c r="H45" t="str">
-        <v/>
-      </c>
-      <c r="I45" t="str">
-        <v/>
-      </c>
-      <c r="J45" t="str">
-        <v/>
-      </c>
-      <c r="K45" t="str">
-        <v/>
-      </c>
-      <c r="L45" t="str">
-        <v/>
-      </c>
-      <c r="M45" t="str">
-        <v/>
+      <c r="B45" s="1">
+        <v>750</v>
+      </c>
+      <c r="C45" s="1">
+        <v>750</v>
+      </c>
+      <c r="D45" s="1">
+        <v>750</v>
+      </c>
+      <c r="E45" s="1">
+        <v>750</v>
+      </c>
+      <c r="F45" s="1">
+        <v>750</v>
+      </c>
+      <c r="G45" s="1">
+        <v>750</v>
+      </c>
+      <c r="H45" s="1">
+        <v>750</v>
+      </c>
+      <c r="I45" s="1">
+        <v>750</v>
+      </c>
+      <c r="J45" s="1">
+        <v>750</v>
+      </c>
+      <c r="K45" s="1">
+        <v>750</v>
+      </c>
+      <c r="L45" s="1">
+        <v>750</v>
+      </c>
+      <c r="M45" s="1">
+        <v>750</v>
       </c>
       <c r="N45" s="1">
         <f>=SUM(B45:M45)</f>
@@ -2612,43 +2612,43 @@
     </row>
     <row r="46">
       <c r="A46" t="str">
-        <v>Familieforsikring</v>
-      </c>
-      <c r="B46" t="str">
-        <v/>
-      </c>
-      <c r="C46" t="str">
-        <v/>
-      </c>
-      <c r="D46" t="str">
-        <v/>
-      </c>
-      <c r="E46" t="str">
-        <v/>
-      </c>
-      <c r="F46" t="str">
-        <v/>
-      </c>
-      <c r="G46" t="str">
-        <v/>
-      </c>
-      <c r="H46" t="str">
-        <v/>
-      </c>
-      <c r="I46" t="str">
-        <v/>
-      </c>
-      <c r="J46" t="str">
-        <v/>
-      </c>
-      <c r="K46" t="str">
-        <v/>
-      </c>
-      <c r="L46" t="str">
-        <v/>
-      </c>
-      <c r="M46" t="str">
-        <v/>
+        <v>Forsikring</v>
+      </c>
+      <c r="B46" s="1">
+        <v>400</v>
+      </c>
+      <c r="C46" s="1">
+        <v>400</v>
+      </c>
+      <c r="D46" s="1">
+        <v>400</v>
+      </c>
+      <c r="E46" s="1">
+        <v>400</v>
+      </c>
+      <c r="F46" s="1">
+        <v>400</v>
+      </c>
+      <c r="G46" s="1">
+        <v>400</v>
+      </c>
+      <c r="H46" s="1">
+        <v>400</v>
+      </c>
+      <c r="I46" s="1">
+        <v>400</v>
+      </c>
+      <c r="J46" s="1">
+        <v>400</v>
+      </c>
+      <c r="K46" s="1">
+        <v>400</v>
+      </c>
+      <c r="L46" s="1">
+        <v>400</v>
+      </c>
+      <c r="M46" s="1">
+        <v>400</v>
       </c>
       <c r="N46" s="1">
         <f>=SUM(B46:M46)</f>
